--- a/artfynd/A 15307-2024 artfynd.xlsx
+++ b/artfynd/A 15307-2024 artfynd.xlsx
@@ -675,57 +675,60 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>116446161</v>
+        <v>116471983</v>
       </c>
       <c r="B2" t="n">
-        <v>97767</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bäckhultemålen (Bäckhultemålen), Sm</t>
+          <t>Kärnebo, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579177</v>
+        <v>579423</v>
       </c>
       <c r="R2" t="n">
-        <v>6324156</v>
+        <v>6324317</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -769,12 +772,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -784,16 +787,11 @@
         <v>116472041</v>
       </c>
       <c r="B3" t="n">
-        <v>57293</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -898,16 +896,11 @@
         <v>116472169</v>
       </c>
       <c r="B4" t="n">
-        <v>57293</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1009,62 +1002,56 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>116447034</v>
+        <v>116472204</v>
       </c>
       <c r="B5" t="n">
-        <v>97767</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bäckhultemålen (Bäckhultemålen), Sm</t>
+          <t>Kärnebo, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579271</v>
+        <v>579226</v>
       </c>
       <c r="R5" t="n">
-        <v>6324234</v>
+        <v>6324147</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1120,15 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>116446893</v>
+        <v>116445931</v>
       </c>
       <c r="B6" t="n">
-        <v>97767</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,22 +1137,22 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bäckhultemålen (Bäckhultemålen), Sm</t>
+          <t>Bäckhultemålen, Bäckhultemålen, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579261</v>
+        <v>579189</v>
       </c>
       <c r="R6" t="n">
-        <v>6324241</v>
+        <v>6324148</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1197,9 +1179,19 @@
           <t>2024-05-01</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1226,15 +1218,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>116446684</v>
+        <v>116446161</v>
       </c>
       <c r="B7" t="n">
-        <v>97767</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,22 +1248,22 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bäckhultemålen (Bäckhultemålen), Sm</t>
+          <t>Bäckhultemålen, Bäckhultemålen, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579252</v>
+        <v>579177</v>
       </c>
       <c r="R7" t="n">
-        <v>6324230</v>
+        <v>6324156</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1332,15 +1319,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>116472393</v>
+        <v>116446684</v>
       </c>
       <c r="B8" t="n">
-        <v>97767</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,34 +1349,22 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kärnebo, Sm</t>
+          <t>Bäckhultemålen, Bäckhultemålen, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579195</v>
+        <v>579252</v>
       </c>
       <c r="R8" t="n">
-        <v>6324181</v>
+        <v>6324230</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1432,80 +1402,70 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>116472204</v>
+        <v>116446893</v>
       </c>
       <c r="B9" t="n">
-        <v>57293</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kärnebo, Sm</t>
+          <t>Bäckhultemålen, Bäckhultemålen, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579226</v>
+        <v>579261</v>
       </c>
       <c r="R9" t="n">
-        <v>6324147</v>
+        <v>6324241</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1549,27 +1509,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>116472112</v>
+        <v>116447034</v>
       </c>
       <c r="B10" t="n">
-        <v>97767</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,12 +1551,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1609,21 +1559,19 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kärnebo, Sm</t>
+          <t>Bäckhultemålen, Bäckhultemålen, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579273</v>
+        <v>579271</v>
       </c>
       <c r="R10" t="n">
-        <v>6324235</v>
+        <v>6324234</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1661,7 +1609,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1680,15 +1627,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>116445931</v>
+        <v>116447097</v>
       </c>
       <c r="B11" t="n">
-        <v>97767</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1715,22 +1657,22 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bäckhultemålen (Bäckhultemålen), Sm</t>
+          <t>Bäckhultemålen, Bäckhultemålen, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579189</v>
+        <v>579262</v>
       </c>
       <c r="R11" t="n">
-        <v>6324148</v>
+        <v>6324230</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1757,19 +1699,9 @@
           <t>2024-05-01</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1796,15 +1728,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>116472459</v>
+        <v>116472112</v>
       </c>
       <c r="B12" t="n">
-        <v>97767</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1831,7 +1758,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1852,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579194</v>
+        <v>579273</v>
       </c>
       <c r="R12" t="n">
-        <v>6324185</v>
+        <v>6324235</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1915,51 +1842,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>116471983</v>
+        <v>116472393</v>
       </c>
       <c r="B13" t="n">
-        <v>57293</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1967,10 +1893,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579423</v>
+        <v>579195</v>
       </c>
       <c r="R13" t="n">
-        <v>6324317</v>
+        <v>6324181</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2011,6 +1937,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2029,42 +1956,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>116472304</v>
+        <v>116472459</v>
       </c>
       <c r="B14" t="n">
-        <v>104854</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2085,10 +2007,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579199</v>
+        <v>579194</v>
       </c>
       <c r="R14" t="n">
-        <v>6324157</v>
+        <v>6324185</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2148,57 +2070,64 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>116447097</v>
+        <v>116472304</v>
       </c>
       <c r="B15" t="n">
-        <v>97767</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bäckhultemålen (Bäckhultemålen), Sm</t>
+          <t>Kärnebo, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579262</v>
+        <v>579199</v>
       </c>
       <c r="R15" t="n">
-        <v>6324230</v>
+        <v>6324157</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2236,18 +2165,19 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2257,12 +2187,7 @@
         <v>116448277</v>
       </c>
       <c r="B16" t="n">
-        <v>100026</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2290,7 +2215,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bäckhultemålen (Bäckhultemålen), Sm</t>
+          <t>Bäckhultemålen, Bäckhultemålen, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">

--- a/artfynd/A 15307-2024 artfynd.xlsx
+++ b/artfynd/A 15307-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116471983</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116472041</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -999,6 +1014,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116472169</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116472204</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1215,6 +1240,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116445931</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1316,6 +1346,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116446161</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1417,6 +1452,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116446684</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1518,6 +1558,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116446893</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1624,6 +1669,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116447034</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1725,6 +1775,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116447097</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1839,6 +1894,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116472112</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1953,6 +2013,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116472393</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2067,6 +2132,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116472459</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2181,6 +2251,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116472304</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2278,8 +2353,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116448277</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>